--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lesehilfe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fragen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aktionen" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paketmatrix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zusatzartikel" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textregeln" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebotsaufbau" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anhänge" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KfW" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Lesehilfe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fragen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aktionen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Paketmatrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Zusatzartikel" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Textregeln" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Angebotsaufbau" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Anhänge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="KfW" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5330,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5358,7 +5358,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>unternehmenspraesentation.pdf</t>
+          <t>Friondo Unternehmenspräsentation.pdf</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -5368,56 +5368,73 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Dateinamen an echte Datei anpassen</t>
+          <t>Unternehmenspräsentation – geht mit jedem Angebot</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>hems_broschuere.pdf</t>
+          <t>Broschüre Ratenkauf.pdf</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>wenn P01 = Ja</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Friondo-HEMS-Broschüre</t>
+          <t>Zahlungsoptionen Barkauf/Finanzierung (Nachtext A) – jedes Angebot</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>cs3800i_broschuere.pdf</t>
+          <t>Friondo HEMS.pdf</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>wenn WP-Paket Pos. 045–054 im Angebot</t>
+          <t>wenn P01 = Ja</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Gerätebroschüre zur angebotenen Wärmepumpe</t>
+          <t>Friondo-HEMS-Broschüre</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>Friondo SpotDynamic.pdf</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>wenn P03 = Ja</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SpotDynamic-Broschüre (dynamischer Stromtarif)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>(weitere Zeilen ergänzen)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Regeln: 'immer' | 'wenn &lt;Frage&gt; = &lt;Antwort&gt;' | 'wenn Pos. &lt;Nr&gt; im Angebot'</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>PDFs in den Ordner anlagen/ legen</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -5330,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5426,15 +5426,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Bosch CS3800iAW.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>wenn WP-Paket Pos. 045–054 im Angebot</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Angebotsbeileger zur angebotenen Wärmepumpe (Gerätebroschüre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>(weitere Zeilen ergänzen)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Regeln: 'immer' | 'wenn &lt;Frage&gt; = &lt;Antwort&gt;' | 'wenn Pos. &lt;Nr&gt; im Angebot'</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>PDFs in den Ordner anlagen/ legen</t>
         </is>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Angebotsaufbau" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Anhänge" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="KfW" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Fragen PV" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fragen KL" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,13 +579,1762 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seite</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fragetext</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Antwortmöglichkeiten</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Anzeigen wenn</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PO01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gebäudeart</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PO02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Baujahr Haus</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PO03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Letzte Dachsanierung</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>leer lassen, wenn unbekannt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PO04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Stromverbrauch inkl. WP &amp; WB in kWh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PO05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PD01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dachart</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Satteldach | Flachdach | Walmdach | Sonstige</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PD02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dachziegel und Ortgang fotografiert?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PD03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gerüstart</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fanggerüst | Vollgerüst | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PD04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dachrinnenhöhe in m</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PD05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Verschattung vorhanden?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PD06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Anzahl Optimierer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nur wenn PD05 = Ja</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PD07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Montage auf mehreren Dachseiten?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PD08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Leitungslänge DC-Kabelweg in m</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PD09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DC-kWp</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DC-Dachmontage</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PD10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PA01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lage ZV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Neue ZV erforderlich?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PA03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Anzahl Felder</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1-Feld | 2-Feld | 3-Feld | 4-Feld | Sonstige</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nur wenn PA02 = Ja</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PA04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ertüchtigung bestehender ZV?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>nur wenn PA02 = Nein</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PA05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Externes APZ-Feld erforderlich?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nur wenn PA04 = Ja</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PA06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HAK-Leitung erneuern?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>nur wenn PA04 = Ja</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PA07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unterverteilung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PA08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tiefenerder vorhanden?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PA09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Leistung Wechselrichter in kW</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PA10</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kapazität Batteriespeicher in kWh</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PA11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Friondo HEMS gewünscht?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PA12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PA13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Friondo SpotDynamic gewünscht?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AC-Elektromontage</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PA14</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Freitext groß</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wiedervorlage am</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seite</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Fragetext</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Antwortmöglichkeiten</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Anzeigen wenn</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KO01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gebäudeart</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EFH | 2FH | REH | RMH | MFH | Gewerbe</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KO02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Baujahr Haus</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KO03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kunde ist Eigentümer?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ja | Nein, Zustimmung des Eigentümers liegt vor | Nein, Zustimmung noch nicht vorhanden</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KO04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Anzahl Außengeräte</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Objekt &amp; Anlage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KO05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Anzahl zu klimatisierender Räume</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>öffnet je Raum einen eigenen Fragenblock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KR01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Raumbezeichnung</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>z. B. Wohnzimmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KR02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lage des Raums</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Keller/Souterrain | Erdgeschoss | 1. OG | 2. OG | 3. OG+ | Dachgeschoss</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KR03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hauptzweck</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hauptsächlich kühlen | kühlen und in der Übergangszeit heizen | regelmäßig heizen und kühlen</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KR04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Montageort Innengerät</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Außenwand | Innenwand | noch nicht bekannt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KR05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entfernung Innen- zu Außengerät</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>bis 3 m | 3–5 m | 6–10 m | 11–15 m | über 16 m</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KR06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kondensatpumpe erforderlich?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Raum {n}</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KR07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Zuordnung zum Außengerät</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>je Raum (KO05)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>es erscheinen nur so viele Optionen wie Außengeräte (KO04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Außengerät</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>KA01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Montageort Außengerät</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auf dem Boden | an der Außenwand | auf einer Terrasse | auf einem Balkon | auf einem Flachdach | auf einem Schrägdach | noch unklar</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Außengerät</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KA02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Montagehöhe</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unter 2 m | 2–4 m | über 5 m</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KE01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Geeignete Stromversorgung nahe Außengerät?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ja | Nein | Unklar</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KE02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Entfernung zum Sicherungskasten</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0–5 m | 6–10 m | 11–15 m | über 16 m</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Elektroinstallation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KE03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Freie Sicherungsplätze vorhanden?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Zugänglichkeit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KZ01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Erreichbarkeit der Montageorte</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vom Boden/Leiter | Gerüst erforderlich | Hubsteiger erforderlich</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wiedervorlage am</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -818,7 +2569,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Rechnungsanschrift korrekt?</t>
+          <t>Rechnungsanschrift identisch mit Ausführungsort?</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -836,7 +2587,11 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>monday-Adresse = Ausführungsort</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -846,12 +2601,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>O07</t>
+          <t>O09</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Korrekte Rechnungsanschrift</t>
+          <t>Rechnungs-Name</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -865,135 +2620,127 @@
           <t>nur wenn O06 = Nein</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>optional – leer = Name des Kunden</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Objektdaten</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>O10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rechnungs-Straße und Hausnummer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nur wenn O06 = Nein</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>O11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rechnungs-PLZ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nur wenn O06 = Nein</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>O12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rechnungs-Ort</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Freitext</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nur wenn O06 = Nein</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Objektdaten</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>O08</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Bemerkung zum Objekt</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Aktueller Energieträger</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Gas | Öl | Nachtspeicher | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Baujahr der alten Heizung</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Aktueller Verbrauch (kWh)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Bei Öl rechnet der Vertriebler Liter in kWh um.</t>
-        </is>
-      </c>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1003,12 +2750,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Lage des Heizraums</t>
+          <t>Aktueller Energieträger</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1018,7 +2765,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
+          <t>Gas | Öl | Nachtspeicher | Sonstiges</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1036,32 +2783,28 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Soll die Wärmepumpe auch ins DG?</t>
+          <t>Baujahr der alten Heizung</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A04 = DG</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Dachzentralen-Block.</t>
+          <t>Steuert Vorbelegung Klima-Bonus (K02).</t>
         </is>
       </c>
     </row>
@@ -1073,96 +2816,100 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
+          <t>Aktueller Verbrauch (kWh)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Bei Öl rechnet der Vertriebler Liter in kWh um.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Heizlast bekannt?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn D01 = Nein</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Entscheidet bei Bekanntsein über das Paket – A03 (kWh) bleibt Pflicht fürs Protokoll</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Alte Anlage</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Sollen die notwendigen Anschlüsse im EG erfolgen?</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn D02 = Nein</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Alte Anlage</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn D03 = Nein</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Heizlast in kW</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nur wenn A14 = Ja</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dezimalzahl, z. B. 8,4 – hat Vorrang vor der kWh-Zuordnung</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1172,34 +2919,30 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Länge der zu verlegenden Leitungen</t>
+          <t>Lage des Heizraums</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Mengenmaske (2 Zahlenfelder)</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Heizung VL/RL (m) | Trinkwasser TWK/TWW/Zirkulation (m)</t>
+          <t>KG | EG | OG | DG | Sonstiges</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>nur wenn D04 = Ja</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Meter je Leitungsart.</t>
-        </is>
-      </c>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1209,28 +2952,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Länge der Erdleitung (m)</t>
+          <t>Soll die Wärmepumpe auch ins DG?</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
+          <t>nur wenn A04 = DG</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
+          <t>Dachzentralen-Block.</t>
         </is>
       </c>
     </row>
@@ -1242,30 +2989,30 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Länge der Fassadenleitung (m)</t>
+          <t>Sind im Keller alle notwendigen Anschlüsse vorhanden?</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Volle Meterzahl.</t>
-        </is>
-      </c>
+          <t>nur wenn D01 = Nein</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1275,30 +3022,30 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
+          <t>Sollen die notwendigen Anschlüsse im EG erfolgen?</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
-        </is>
-      </c>
+          <t>nur wenn D02 = Nein</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1308,12 +3055,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Öl-Tankentsorgung erforderlich?</t>
+          <t>Können die Leitungen durch den Schacht verlegt werden und ist dieser frei?</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1328,7 +3075,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A01 = Öl</t>
+          <t>nur wenn D03 = Nein</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
@@ -1341,30 +3088,34 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Art des Öltanks</t>
+          <t>Länge der zu verlegenden Leitungen</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Mengenmaske (2 Zahlenfelder)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Stahl | Kunststoff | Unterirdisch</t>
+          <t>Heizung VL/RL (m) | Trinkwasser TWK/TWW/Zirkulation (m)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A07 = Ja</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr"/>
+          <t>nur wenn D04 = Ja</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Meter je Leitungsart.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1374,30 +3125,30 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Wie groß ist der Tank?</t>
+          <t>Länge der Erdleitung (m)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
-        </is>
-      </c>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>nur wenn A08 = Stahl oder Kunststoff</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+          <t>nur wenn A04 = KG oder EG, oder (A04 = DG und D01 = Nein)</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Berechnet wird Eingabe − 3 m (nie unter 0).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1407,30 +3158,30 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Solarthermie vorhanden?</t>
+          <t>Länge der Fassadenleitung (m)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
-        </is>
-      </c>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
+          <t>nur wenn A04 = OG, oder (A04 = DG und D01 = Ja)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Volle Meterzahl.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1440,24 +3191,20 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>PV-Anlage vorhanden?</t>
+          <t>Leitungslänge zwischen Hauseinführung und WP-Inneneinheit (m)?</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein | Ist geplant</t>
-        </is>
-      </c>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>immer</t>
@@ -1465,7 +3212,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Info.</t>
+          <t>Anschlussleitung Inneneinheit; berechnet wird Eingabe − 5 m (nie unter 0).</t>
         </is>
       </c>
     </row>
@@ -1477,434 +3224,434 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Öl-Tankentsorgung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn A01 = Öl</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Art des Öltanks</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Stahl | Kunststoff | Unterirdisch</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn A07 = Ja</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Wie groß ist der Tank?</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>bis 3.000 L | bis 4.000 L | bis 5.000 L | bis 6.000 L | bis 7.000 L | bis 8.000 L | bis 9.000 L | ab 9.000 L</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stemmarbeiten für einen Durchgang benötigt?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nur wenn A08 = Stahl oder Kunststoff</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Solarthermie vorhanden?</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Ja, soll übernommen werden | Ja, soll stillgelegt werden | Nein</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>PV-Anlage vorhanden?</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein | Ist geplant</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Info.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Alte Anlage</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>A12</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Bemerkung zur alten Anlage</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>N01</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Art der Wärmepumpe</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Luft/Wasser | Luft/Luft | Sole/Wasser | Split | Sonstiges</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>N02</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Warmwasser über die Wärmepumpe?</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Steuert Paketvariante + Überschrift Block 1.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>N03</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Größe des Warmwasserspeichers</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>bis 200 l | 300 l | mehr als 300 l</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>nur wenn N02 = Ja</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>AWM-Pakete haben 180-l-Speicher integriert.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>N04</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Aufstellort der Wärmepumpe</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Boden | Garagendach | Sonstiges</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>N05</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Durchführung durch Bitumen?</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>nur wenn N04 = Garagendach</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>N06</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Größe des Pufferspeichers</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Wie viele Heizkreise?</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Verteilsystem</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Heizkörpertausch erforderlich?</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H02 = Heizkörper oder beides</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>H04</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Mengenmaske</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>S | M | L | XL</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H03 = Ja</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Leer/0 = entfällt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>H05</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>H06</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Anzahl Heizkreisverteiler</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1914,148 +3661,148 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Gruppen je Heizkreisverteiler {n}</t>
+          <t>Wie viele Heizkreise?</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Wiederholfeld</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3 | mehr als 3</t>
+        </is>
+      </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Ein Feld pro Verteiler aus H06.</t>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Lage der Zählerverteilung</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wärmemengenzähler erforderlich?</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>bei mehr als einer Wohneinheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Anzahl Wärmemengenzähler</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>nur wenn H08 = Ja</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Verteilsystem</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>Info (außer Sonstiges).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Wie viele Felder?</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn E02 = Ja</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Friondo HEMS gewünscht?</t>
+          <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2070,7 +3817,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
@@ -2078,54 +3825,54 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
+          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Auswahl</t>
+          <t>Mengenmaske</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>S | M | L | XL</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>immer</t>
+          <t>nur wenn H03 = Ja</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Löst Vollmacht-Seite aus.</t>
+          <t>Leer/0 = entfällt.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Friondo</t>
+          <t>Heizverteilung</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Friondo SpotDynamic gewünscht?</t>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2140,156 +3887,560 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
-        </is>
-      </c>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>K01</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
-        </is>
-      </c>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Anzahl Heizkreisverteiler</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>K02</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>nur bei Selbstnutzung</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Gruppen je Heizkreisverteiler {n}</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Wiederholfeld</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Förderung</t>
+          <t>Elektro/ZV</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>K03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+          <t>Lage der Zählerverteilung</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Betragseingabe</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
+          <t>Info (außer Sonstiges).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Wie viele Felder?</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>nur wenn E02 = Ja</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Unterverteilung erforderlich?</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>nur wenn E02 = Nein</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MID-Zwischenzähler erforderlich?</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>nur wenn E04 = Ja</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Friondo HEMS gewünscht?</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Löst Vollmacht-Seite aus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Friondo SpotDynamic gewünscht?</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Löst Vollmacht-Seite aus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>Förderung</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>K01</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>nur wenn O01 = 2FH oder MFH</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>K02</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>K03</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Betragseingabe</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>K04</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Minderjähriges Kind im Haushalt?</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>nur wenn K03 ausgefüllt</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>10.000 € Abzug vom Einkommen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Einschätzung des Kunden</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>heiß | warm | kalt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Einschätzung</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wiedervorlage am</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
       </c>
     </row>
@@ -2304,7 +4455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3886,7 +6037,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>E04–E06 folgen</t>
+          <t>E04/E05 folgen (Unterverteilung)</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr"/>
@@ -4090,6 +6241,274 @@
           <t>Innendienst-Liste</t>
         </is>
       </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>– (Paket weiter über A03/kWh)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>bis 15,9</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ab 16</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 126 ×1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Stemmarbeiten für einen Durchgang (Öl-Zweig)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>H09 folgt</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 096 × Anzahl (kein EP)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wärmemengenzähler als normale Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 152 ×1; E05 folgt</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Unterverteilung</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Artikel: Z23 ×1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MID-Zwischenzähler</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>heiß / warm / kalt</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Startwerte der Angebotsverfolgung – keine Artikel</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4102,7 +6521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4138,6 +6557,11 @@
           <t>WW 300 l (N03)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Heizlast (A15)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -4165,6 +6589,11 @@
           <t>Pos. 050 + Pos. 065</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bis 5,9 kW</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -4192,6 +6621,11 @@
           <t>Pos. 051 + Pos. 065</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,0 – 7,9 kW</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -4219,6 +6653,11 @@
           <t>Pos. 052 + Pos. 065</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,0 – 9,9 kW</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -4246,6 +6685,11 @@
           <t>Pos. 053 + Pos. 065</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10,0 – 12,9 kW</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4271,6 +6715,11 @@
       <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Pos. 054 + Pos. 065</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13,0 – 15,9 kW</t>
         </is>
       </c>
     </row>
@@ -4285,7 +6734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4905,6 +7354,34 @@
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Zusätzlicher Zählerschrank zur bestehenden Verteilung. inkl. APZ Feld, SLS Schalter 50A, AC Überspannungsschutz, 1x4Pol. FI Schutzschalter, LS Automaten, Klemmstein, Verdrahtungsarbeiten, Hauptzuleitung vom HAK bis zum neuen Zählerschrank und Verbindung zur bestehenden Verteilung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Z23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Privater Unterzähler inkl. Anbindung</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>217</v>
+      </c>
+      <c r="E24" t="n">
+        <v>155</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3-Phasen Stromzähler mit MID zur privaten Verbrauchsmessung einer Wohneinheit</t>
         </is>
       </c>
     </row>
@@ -5090,7 +7567,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Pos. 005 · 006 · 007 (EP) · 008 · Erd-/Fassadenleitung (A05/A06) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D05, Pos. 141 aus D03) · Heizkreise (H01)</t>
+          <t>Pos. 005 · 006 · 007 (EP) · 008 · Erd-/Fassadenleitung (A05/A06) · Anschlussleitung Inneneinheit (Pos. 103 aus A13) · Dachzentralen-Leitungen (Pos. 139/140 aus D05, Pos. 141 aus D03) · Heizkreise (H01) · Wärmemengenzähler: Pos. 096 × Anzahl (H09)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -5156,7 +7633,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG)</t>
+          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG) · ggf. Stemmarbeiten Pos. 126</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -5200,7 +7677,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Pos. 011 · ZV: 104 / Z22 bzw. 149 / 150 / 153</t>
+          <t>Pos. 011 · ZV: 104 / Z22 bzw. 149 / 150 / 153 · Unterverteilung: Pos. 152 + Z23 (E04/E05)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -656,7 +656,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -679,13 +678,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,7 +705,6 @@
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>immer</t>
@@ -741,13 +737,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -770,13 +764,11 @@
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -809,7 +801,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -842,7 +833,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -875,7 +865,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -898,13 +887,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -937,7 +924,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -960,13 +946,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>nur wenn PD05 = Ja</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -999,7 +983,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1022,13 +1005,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1051,13 +1032,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1080,13 +1059,11 @@
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1119,7 +1096,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1152,7 +1128,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1185,7 +1160,6 @@
           <t>nur wenn PA02 = Ja</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1218,7 +1192,6 @@
           <t>nur wenn PA02 = Nein</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1251,7 +1224,6 @@
           <t>nur wenn PA04 = Ja</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1284,7 +1256,6 @@
           <t>nur wenn PA04 = Ja</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1317,7 +1288,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1350,7 +1320,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1373,13 +1342,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1402,13 +1369,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1441,7 +1406,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1474,7 +1438,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1507,7 +1470,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1530,13 +1492,11 @@
           <t>Freitext groß</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1596,7 +1556,6 @@
           <t>Datum</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>immer</t>
@@ -1690,7 +1649,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1713,13 +1671,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1752,7 +1708,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1785,7 +1740,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1808,7 +1762,6 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>immer</t>
@@ -1823,7 +1776,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1841,7 +1794,6 @@
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>je Raum (KO05)</t>
@@ -1856,7 +1808,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1884,12 +1836,11 @@
           <t>je Raum (KO05)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1917,12 +1868,11 @@
           <t>je Raum (KO05)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1950,12 +1900,11 @@
           <t>je Raum (KO05)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1983,12 +1932,11 @@
           <t>je Raum (KO05)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2016,12 +1964,11 @@
           <t>je Raum (KO05)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Raum {n}</t>
+          <t>Räume</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2086,7 +2033,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2119,7 +2065,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2152,7 +2097,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2185,7 +2129,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2218,7 +2161,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2251,7 +2193,6 @@
           <t>immer</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2311,7 +2252,6 @@
           <t>Datum</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>immer</t>
@@ -2647,13 +2587,11 @@
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>nur wenn O06 = Nein</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2676,13 +2614,11 @@
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>nur wenn O06 = Nein</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2705,13 +2641,11 @@
           <t>Freitext</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>nur wenn O06 = Nein</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2899,7 +2833,6 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>nur wenn A14 = Ja</t>
@@ -3346,7 +3279,6 @@
           <t>nur wenn A08 = Stahl oder Kunststoff</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3748,13 +3680,11 @@
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>nur wenn H08 = Ja</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4088,7 +4018,6 @@
           <t>nur wenn E02 = Nein</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4121,7 +4050,6 @@
           <t>nur wenn E04 = Ja</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4432,7 +4360,6 @@
           <t>Datum</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>immer</t>
@@ -6258,7 +6185,6 @@
           <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6276,7 +6202,6 @@
           <t>– (Paket weiter über A03/kWh)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6294,7 +6219,6 @@
           <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6312,7 +6236,6 @@
           <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6352,7 +6275,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6370,7 +6292,6 @@
           <t>H09 folgt</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6388,7 +6309,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6450,7 +6370,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6490,7 +6409,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6508,7 +6426,6 @@
           <t>Startwerte der Angebotsverfolgung – keine Artikel</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -5430,10 +5430,14 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AWE-Paket lt. Paketmatrix + Pos. 065 ×1</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr"/>
+          <t>AWE-Paket lt. Paketmatrix (inkl. Pos. 065)</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Pos. 065 kommt AUSSCHLIESSLICH aus der Paketmatrix-Spalte WW 300 l – hier keine eigene Artikel-Anweisung</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -2274,7 +2274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3487,37 +3487,41 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Neue Anlage</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Aufstellort der Wärmepumpe</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Farbe der Außeneinheit?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Boden | Garagendach | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Weiß | Schwarz</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: Pos. 030 (weiß) / Pos. 031 (schwarz)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3527,12 +3531,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>N05</t>
+          <t>N04</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Durchführung durch Bitumen?</t>
+          <t>Aufstellort der Wärmepumpe</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3542,12 +3546,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Ja | Nein</t>
+          <t>Boden | Garagendach | Sonstiges</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>nur wenn N04 = Garagendach</t>
+          <t>immer</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -3560,197 +3564,201 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>N05</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Durchführung durch Bitumen?</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>nur wenn N04 = Garagendach</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>N06</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Größe des Pufferspeichers</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>50 l | 100 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Wie viele Heizkreise?</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>1 | 2 | 3 | mehr als 3</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
-        </is>
-      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>nur wenn Klasse = 4 kW oder 6 kW oder 7 kW oder 10 kW oder 13 kW</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Neue Anlage</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Größe des Pufferspeichers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>70 l | 200 l | 300 l | 500 l | mehr als 500 l</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nur wenn Klasse = 15 kW</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Serie CS8800i: 70 l = AWMB (integriert), sonst AWE + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Wie viele Heizkreise?</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>1 | 2 | 3 | mehr als 3</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Ein Heizkreis ist im WP-Paket enthalten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>H08</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Wärmemengenzähler erforderlich?</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>bei mehr als einer Wohneinheit</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Heizverteilung</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>H09</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Anzahl Wärmemengenzähler</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Zahleneingabe</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>nur wenn H08 = Ja</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Verteilsystem</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Heizverteilung</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Heizkörpertausch erforderlich?</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>nur wenn H02 = Heizkörper oder beides</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3760,34 +3768,30 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
+          <t>Verteilsystem</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Mengenmaske</t>
+          <t>Auswahl</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>S | M | L | XL</t>
+          <t>Heizkörper | Fußbodenheizung | Heizkörper und Fußbodenheizung | Sonstiges</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>nur wenn H03 = Ja</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>Leer/0 = entfällt.</t>
-        </is>
-      </c>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3797,12 +3801,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>FBH-Heizkreisverteiler einregulierbar?</t>
+          <t>Heizkörpertausch erforderlich?</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3817,7 +3821,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+          <t>nur wenn H02 = Heizkörper oder beides</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
@@ -3830,26 +3834,34 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Anzahl Heizkreisverteiler</t>
+          <t>Anzahl Heizkörper je Größe (S/M/L/XL)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Zahleneingabe</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
+          <t>Mengenmaske</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>S | M | L | XL</t>
+        </is>
+      </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>nur wenn H05 = Nein</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
+          <t>nur wenn H03 = Ja</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Leer/0 = entfällt.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -3859,100 +3871,92 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>FBH-Heizkreisverteiler einregulierbar?</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn H02 = Fußbodenheizung oder beides</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Anzahl Heizkreisverteiler</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Zahleneingabe</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>nur wenn H05 = Nein</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Heizverteilung</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
           <t>H07</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Gruppen je Heizkreisverteiler {n}</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Wiederholfeld</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>nur wenn H05 = Nein</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Ein Feld pro Verteiler aus H06.</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Lage der Zählerverteilung</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>KG | EG | OG | DG | Sonstiges</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Info (außer Sonstiges).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Elektro/ZV</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Muss die Zählerverteilung erneuert werden?</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -3962,162 +3966,162 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Lage der Zählerverteilung</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>KG | EG | OG | DG | Sonstiges</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Info (außer Sonstiges).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Muss die Zählerverteilung erneuert werden?</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Elektro/ZV</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>E03</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Wie viele Felder?</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>2-Feld | 3-Feld | 4-Feld und mehr</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>nur wenn E02 = Ja</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Elektro/ZV</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Unterverteilung erforderlich?</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>nur wenn E02 = Nein</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Elektro/ZV</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>MID-Zwischenzähler erforderlich?</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>nur wenn E04 = Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Friondo</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Friondo HEMS gewünscht?</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Friondo</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>P02</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>iMSys inkl. Smart Meter gewünscht?</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>immer</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Löst Vollmacht-Seite aus.</t>
         </is>
       </c>
     </row>
@@ -4129,106 +4133,102 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Friondo HEMS gewünscht?</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>iMSys inkl. Smart Meter gewünscht?</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>immer</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Löst Vollmacht-Seite aus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Friondo</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Friondo SpotDynamic gewünscht?</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Löst Vollmacht-Seite aus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>K01</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Ja | Nein</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>nur wenn O01 = 2FH oder MFH</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Förderung</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>K02</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Auswahl</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>nur bei Selbstnutzung</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Vorbelegt aus A01 + A02, änderbar.</t>
         </is>
       </c>
     </row>
@@ -4240,28 +4240,32 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>K03</t>
+          <t>K01</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+          <t>Bewohnt der Eigentümer eine Wohneinheit selbst?</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Betragseingabe</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr"/>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Ja | Nein</t>
+        </is>
+      </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>nur bei Selbstnutzung</t>
+          <t>nur wenn O01 = 2FH oder MFH</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Leer oder über 50.000 € = kein Bonus.</t>
+          <t>EFH/REH/RMH: automatisch Ja. Gewerbe: automatisch Nein.</t>
         </is>
       </c>
     </row>
@@ -4273,99 +4277,169 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
+          <t>K02</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Welche Heizung wird ersetzt? (Klima-Bonus)</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Auswahl</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Öl-, Kohle-, Gasetagen- oder Nachtspeicherheizung, funktionstüchtig | Gas- oder Biomasseheizung, mind. 20 Jahre, funktionstüchtig | Andere / jüngere Heizung / Neubau</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Vorbelegt aus A01 + A02, änderbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>K03</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Zu versteuerndes Haushaltsjahreseinkommen (€)</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Betragseingabe</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>nur bei Selbstnutzung</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Leer oder über 50.000 € = kein Bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Förderung</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
           <t>K04</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Minderjähriges Kind im Haushalt?</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Ja | Nein</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>nur wenn K03 ausgefüllt</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>10.000 € Abzug vom Einkommen.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Einschätzung des Kunden</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Auswahl</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>heiß | warm | kalt</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Startwert der Angebotsverfolgung (Hot-Ampel)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Einschätzung</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>S02</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Wiedervorlage am</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>optional – leer lassen, wenn keine Wiedervorlage nötig</t>
         </is>
@@ -4382,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4591,33 +4665,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>über 31.000 kWh</t>
+          <t>31.001 – 37.000 kWh</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
+          <t>Leistungsklasse 15 kW merken (Serie CS8800i)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>über 37.000 kWh</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>KG oder EG</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>A05 (Erdleitung) folgt</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4627,12 +4700,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OG</t>
+          <t>KG oder EG</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>A06 (Fassadenleitung) folgt</t>
+          <t>A05 (Erdleitung) folgt</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
@@ -4645,19 +4718,15 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>OG</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Dachzentralen-Block (D01–D05) folgt; Artikel: Pos. 163 ×1</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Pos. 163 (Rückbau/Stilllegung Abgasanlage Dachzentrale) immer, wenn alte Anlage im DG</t>
-        </is>
-      </c>
+          <t>A06 (Fassadenleitung) folgt</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4667,99 +4736,103 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Dachzentralen-Block (D01–D05) folgt; Artikel: Pos. 163 ×1</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Pos. 163 (Rückbau/Stilllegung Abgasanlage Dachzentrale) immer, wenn alte Anlage im DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Lage des Heizraums zzt. nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>A05</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Artikel: Pos. 102 × (Eingabe − 3), nie unter 0</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>3 m im Fundament enthalten; Eingabe 8 → 5 m berechnet. Bei Ergebnis 0: keine Position.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>A06</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 134 × Eingabe</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>volle Meterzahl</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Meterzahl</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Artikel: Pos. 103 × (Eingabe − 5), nie unter 0</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>5 m sind in Pos. 006 (Montagematerial) enthalten; Eingabe 8 → 3 m berechnet. Ergebnis 0 = keine Position.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>– (Anlage bleibt im DG; A06 Fassadenleitung wird gestellt)</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4769,37 +4842,37 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>– (Anlage bleibt im DG; A06 Fassadenleitung wird gestellt)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>D02 folgt; A05 Erdleitung wird gestellt (neuer Heizraum unten)</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Annahme: Aufstellung unten → Erdleitung</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -4809,33 +4882,33 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>D03 folgt</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 141 ×1 (Montage-/Installationsarbeiten Anschlüsse EG)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4845,33 +4918,33 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 141 ×1 (Montage-/Installationsarbeiten Anschlüsse EG)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>D04 folgt</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>D05 folgt</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -4881,33 +4954,33 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>D05 folgt</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Leitungsführung Dachzentrale nicht konfigurierbar (Schacht nicht nutzbar)</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Heizung VL/RL (m)</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 139 × Eingabe</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4917,33 +4990,33 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>Heizung VL/RL (m)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 139 × Eingabe</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>Trinkwasser TWK/TWW/Zirkulation (m)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 140 × Eingabe</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>A08 folgt</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -4953,33 +5026,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>A08 folgt</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Stahl oder Kunststoff</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>A09 folgt</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4989,33 +5062,33 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
+          <t>Stahl oder Kunststoff</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>A09 folgt</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>Unterirdisch</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 107 ×1 (Größenfrage entfällt)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Kunststoff, bis 3.000 L</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z01 ×1</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -5025,12 +5098,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 4.000 L</t>
+          <t>Kunststoff, bis 3.000 L</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z02 ×1</t>
+          <t>Artikel: Z01 ×1</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
@@ -5043,12 +5116,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 5.000 L</t>
+          <t>Kunststoff, bis 4.000 L</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z03 ×1</t>
+          <t>Artikel: Z02 ×1</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr"/>
@@ -5061,12 +5134,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 6.000 L</t>
+          <t>Kunststoff, bis 5.000 L</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z04 ×1</t>
+          <t>Artikel: Z03 ×1</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr"/>
@@ -5079,12 +5152,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 7.000 L</t>
+          <t>Kunststoff, bis 6.000 L</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z05 ×1</t>
+          <t>Artikel: Z04 ×1</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
@@ -5097,12 +5170,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 8.000 L</t>
+          <t>Kunststoff, bis 7.000 L</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z06 ×1</t>
+          <t>Artikel: Z05 ×1</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
@@ -5115,12 +5188,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Kunststoff, bis 9.000 L</t>
+          <t>Kunststoff, bis 8.000 L</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z07 ×1</t>
+          <t>Artikel: Z06 ×1</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr"/>
@@ -5133,12 +5206,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 3.000 L</t>
+          <t>Kunststoff, bis 9.000 L</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z08 ×1</t>
+          <t>Artikel: Z07 ×1</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr"/>
@@ -5151,12 +5224,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 4.000 L</t>
+          <t>Stahl, bis 3.000 L</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z09 ×1</t>
+          <t>Artikel: Z08 ×1</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr"/>
@@ -5169,12 +5242,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 5.000 L</t>
+          <t>Stahl, bis 4.000 L</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z10 ×1</t>
+          <t>Artikel: Z09 ×1</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr"/>
@@ -5187,12 +5260,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 6.000 L</t>
+          <t>Stahl, bis 5.000 L</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z11 ×1</t>
+          <t>Artikel: Z10 ×1</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr"/>
@@ -5205,12 +5278,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 7.000 L</t>
+          <t>Stahl, bis 6.000 L</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z12 ×1</t>
+          <t>Artikel: Z11 ×1</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr"/>
@@ -5223,12 +5296,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 8.000 L</t>
+          <t>Stahl, bis 7.000 L</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z13 ×1</t>
+          <t>Artikel: Z12 ×1</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr"/>
@@ -5241,12 +5314,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Stahl, bis 9.000 L</t>
+          <t>Stahl, bis 8.000 L</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Z14 ×1</t>
+          <t>Artikel: Z13 ×1</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr"/>
@@ -5259,33 +5332,33 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>Stahl, bis 9.000 L</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Artikel: Z14 ×1</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>ab 9.000 L</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Größe des Öl-Tanks nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Ja, soll übernommen werden</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Übernahme)</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5295,12 +5368,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Ja, soll stillgelegt werden</t>
+          <t>Ja, soll übernommen werden</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Stilllegung)</t>
+          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Übernahme)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
@@ -5313,33 +5386,33 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>Ja, soll stillgelegt werden</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Stilllegung)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>N01</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Luft/Wasser</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>weiter</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -5349,37 +5422,33 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
+          <t>Luft/Wasser</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>weiter</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
           <t>Luft/Luft / Sole/Wasser / Split / Sonstiges</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Wärmepumpen-Art nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>N02</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Paketvariante 'mit Warmwasser'; Überschrift Block 1 Variante 2</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>N03 folgt</t>
-        </is>
-      </c>
+      <c r="D53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -5389,33 +5458,37 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Paketvariante 'mit Warmwasser'; Überschrift Block 1 Variante 2</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>N03 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Paketvariante 'ohne Warmwasser' (AWE)</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>N03</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>bis 200 l</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>AWM-Paket lt. Paketmatrix</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -5425,19 +5498,15 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>300 l</t>
+          <t>bis 200 l</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AWE-Paket lt. Paketmatrix (inkl. Pos. 065)</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Pos. 065 kommt AUSSCHLIESSLICH aus der Paketmatrix-Spalte WW 300 l – hier keine eigene Artikel-Anweisung</t>
-        </is>
-      </c>
+          <t>AWM-Paket lt. Paketmatrix</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -5447,33 +5516,37 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
+          <t>300 l</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>AWE-Paket lt. Paketmatrix (inkl. Pos. 065)</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Pos. 065 kommt AUSSCHLIESSLICH aus der Paketmatrix-Spalte WW 300 l – hier keine eigene Artikel-Anweisung</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
           <t>mehr als 300 l</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: WW-Speichergröße zu groß</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 010 ×1</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -5483,19 +5556,15 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Garagendach</t>
+          <t>Boden</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 132 ×1 + Pos. 135 ×1 als EP</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>N05 folgt</t>
-        </is>
-      </c>
+          <t>Artikel: Pos. 010 ×1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5505,33 +5574,37 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
+          <t>Garagendach</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 132 ×1 + Pos. 135 ×1 als EP</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>N05 folgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Aufstellort zzt. nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>N05</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 133 ×1</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5541,33 +5614,33 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 133 ×1</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>N05</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>50 l / 100 l / 200 l</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Z15 / Z16 / Z17 ×1</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5577,12 +5650,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>300 l / 500 l</t>
+          <t>50 l / 100 l / 200 l</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 098 / Pos. 099 ×1</t>
+          <t>Artikel: Z15 / Z16 / Z17 ×1</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
@@ -5595,33 +5668,33 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>300 l / 500 l</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 098 / Pos. 099 ×1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>mehr als 500 l</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>– (im WP-Paket enthalten)</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -5631,12 +5704,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 090 ×1</t>
+          <t>– (im WP-Paket enthalten)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr"/>
@@ -5649,12 +5722,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 090 ×2</t>
+          <t>Artikel: Pos. 090 ×1</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr"/>
@@ -5667,33 +5740,33 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 090 ×2</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
           <t>mehr als 3</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Anzahl der Heizkreise nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Heizkörper</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>H03/H04 folgen</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5703,12 +5776,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Fußbodenheizung</t>
+          <t>Heizkörper</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>H05–H07 folgen</t>
+          <t>H03/H04 folgen</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -5721,12 +5794,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Heizkörper und Fußbodenheizung</t>
+          <t>Fußbodenheizung</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>beide Blöcke nacheinander</t>
+          <t>H05–H07 folgen</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -5739,33 +5812,33 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
+          <t>Heizkörper und Fußbodenheizung</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>beide Blöcke nacheinander</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Verteilsystem nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>H04 folgt</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -5775,55 +5848,55 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>H04 folgt</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>H04</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Anzahl S / M / L / XL</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Artikel: Z18 / Pos. 130 / Z19 / Pos. 131 × Anzahl</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>zusätzlich Pos. 129 × Gesamtanzahl</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>H05</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -5833,55 +5906,51 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>H06 + H07 folgen</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>H06</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Anzahl</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 108 × Anzahl Verteiler</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>H07</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>bis 4 / 5–8 / 9–14 Gruppen</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Artikel: Z20 / Pos. 109 / Z21 ×1 je Verteiler</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>gleiche Größen zusammenfassen</t>
-        </is>
-      </c>
+      <c r="D80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -5891,33 +5960,37 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
+          <t>bis 4 / 5–8 / 9–14 Gruppen</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Artikel: Z20 / Pos. 109 / Z21 ×1 je Verteiler</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>gleiche Größen zusammenfassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
           <t>über 14 Gruppen</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Gruppenanzahl Heizkreisverteiler nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>KG / EG / OG / DG</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>– (nur Protokoll)</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -5927,33 +6000,33 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
+          <t>KG / EG / OG / DG</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>– (nur Protokoll)</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
           <t>Sonstiges</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: ZV-Lage nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>E03 folgt</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -5963,33 +6036,33 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>E03 folgt</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>E04/E05 folgen (Unterverteilung)</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>2-Feld</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>Artikel: Pos. 104 ×1</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -5999,12 +6072,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>3-Feld</t>
+          <t>2-Feld</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Artikel: Z22 ×1</t>
+          <t>Artikel: Pos. 104 ×1</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -6017,176 +6090,177 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>3-Feld</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Artikel: Z22 ×1</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>4-Feld und mehr</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>AMPEL: individuell – Grund: Zählerverteilung nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>P01</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>Artikel: Pos. 015 ×1</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>P02</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 016 ×1</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>aktiviert Vollmacht-Seite</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>Artikel: Pos. 017 ×1</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>aktiviert Vollmacht-Seite</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Gruppen-Trigger</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>mind. ein Ja bei P01–P03</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Artikel: Pos. 014 ×1 direkt davor</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>599 € einmalig</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Grundpaket</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>immer</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>Pos. 003, 005, 006, 007 (EP), 008, 009, 011, 012, 013</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Einsortierung lt. Angebotsaufbau</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>O01–O08 / K01–K04</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Objekt-/Förderangaben</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>keine Artikel – KfW-Ableitung lt. Blatt KfW</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>Ampel-Auswertung</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>mind. ein AMPEL-Treffer</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>Erfassung = 'Individuell' (orange) mit Grundliste; sonst 'Konfigurierbar' (grün)</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Innendienst-Liste</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>A14</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
@@ -6198,29 +6272,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>– (Paket weiter über A03/kWh)</t>
+          <t>A15 folgt – Heizlast hat Vorrang vor der kWh-Zuordnung</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>bis 15,9</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
+          <t>– (Paket weiter über A03/kWh)</t>
         </is>
       </c>
     </row>
@@ -6232,58 +6306,53 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ab 16</t>
+          <t>bis 15,9</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
+          <t>Leistungsklasse lt. Paketmatrix-Spalte „Heizlast“ merken (Vorrang vor A03)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>16,0 – 18,5</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 126 ×1</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Stemmarbeiten für einen Durchgang (Öl-Zweig)</t>
+          <t>Leistungsklasse 15 kW merken (Serie CS8800i, Vorrang vor A03)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>ab 18,6</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>AMPEL: individuell – Grund: Leistungsklasse zu hoch</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6293,14 +6362,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>H09 folgt</t>
+          <t>Artikel: Pos. 126 ×1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Stemmarbeiten für einen Durchgang (Öl-Zweig)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6317,68 +6391,63 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Anzahl</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 096 × Anzahl (kein EP)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Wärmemengenzähler als normale Position</t>
+          <t>H09 folgt</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Artikel: Pos. 152 ×1; E05 folgt</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Unterverteilung</t>
+          <t>–</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Anzahl</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Artikel: Pos. 096 × Anzahl (kein EP)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wärmemengenzähler als normale Position</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6388,19 +6457,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Artikel: Z23 ×1</t>
+          <t>Artikel: Pos. 152 ×1; E05 folgt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>MID-Zwischenzähler</t>
+          <t>Unterverteilung</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6417,19 +6486,208 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Artikel: Z23 ×1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>MID-Zwischenzähler</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>heiß / warm / kalt</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Startwerte der Angebotsverfolgung – keine Artikel</t>
         </is>
       </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>N08</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Weiß</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 030 ×1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Außeneinheit AW 15 O-T (Serie CS8800i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>N08</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Schwarz</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 031 ×1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Außeneinheit AW 15 O-TB (Serie CS8800i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>70 l</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 055 ×1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AWMB-Inneneinheit mit integriertem 70-l-Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>200 l</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Z17 ×1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>300 l</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Pos. 098 ×1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>500 l</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Artikel: Pos. 056 ×1 + Pos. 099 ×1</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AWE-Inneneinheit + externer Puffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>mehr als 500 l</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6442,7 +6700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6497,7 +6755,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Pos. 045 (CS3800i AWM 4)</t>
+          <t>Pos. 045 (CS3800i AWM 4) + Pos. 067</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -6529,7 +6787,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Pos. 046 (AWM 6)</t>
+          <t>Pos. 046 (AWM 6) + Pos. 067</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -6561,7 +6819,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Pos. 047 (AWM 7)</t>
+          <t>Pos. 047 (AWM 7) + Pos. 067</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -6593,7 +6851,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Pos. 048 (AWM 10)</t>
+          <t>Pos. 048 (AWM 10) + Pos. 067</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -6625,7 +6883,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Pos. 049 (AWM 13)</t>
+          <t>Pos. 049 (AWM 13) + Pos. 067</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -6641,6 +6899,38 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>13,0 – 15,9 kW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15 kW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>31.001 – 37.000 kWh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lt. Puffer-/Farbfrage (AWMB/AWE, Serie CS8800i)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lt. Puffer-/Farbfrage (Serie CS8800i)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lt. Puffer-/Farbfrage + Warmwasserbereitung fix</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16,0 – 18,5 kW</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7756,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003</t>
+          <t>WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003 · Serie CS8800i: 030 / 031 · 055 / 056 (N07/N08) · 067</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">

--- a/konfigurator_logik_v5.xlsx
+++ b/konfigurator_logik_v5.xlsx
@@ -18,6 +18,7 @@
     <sheet name="KfW" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Fragen PV" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Fragen KL" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Vermerke" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2268,6 +2269,55 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bedingung</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Platzierung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vermerk zur Heizungsumverlegung
+Im Rahmen des vorliegenden Angebots ist vorgesehen, die bestehende Heizungsanlage aus dem Dachgeschoss in das Kellergeschoss zu verlegen. Die finale Ausführung kann erst im Zuge der detaillierten Feinplanung verbindlich festgelegt werden. Voraussetzung hierfür ist die eindeutige Klärung der hydraulischen Anbindung im Kellergeschoss. Insbesondere müssen geeignete Anschlusspunkte für Heizungs-Vorlauf und -Rücklauf sowie für die Warmwasserversorgung und eine gegebenenfalls erforderliche Zirkulationsleitung vorhanden sein. Für die Kalkulation dieses Angebots wird davon ausgegangen, dass entsprechende Übergabepunkte im Kellergeschoss selbst oder alternativ im direkt darüberliegenden Geschoss vorhanden sind und für die Anbindung genutzt werden können. Die erforderlichen baulichen Maßnahmen zur Leitungsführung einschließlich der Öffnung von Fliesenflächen, Trockenbaukonstruktionen sowie ggf. die Nutzung eines geeigneten Schachtes mit Durchführung in das Kellergeschoss wurden bereits berücksichtigt und sind Bestandteil der Kalkulation. Diese Voraussetzungen werden bauseitig als gegeben angenommen.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nur wenn A04 = DG und D01 = Nein</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ende Positionsteil</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5373,10 +5423,14 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Übernahme)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
+          <t>Warmwasser lt. Paketmatrix-Übersteuerung: AWE-Variante + bivalenter 390-l-Solarspeicher (Engine, keine eigene Artikel-Anweisung); N03 entfällt</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Solarthermie-Übernahme (v9)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5391,10 +5445,14 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>AMPEL: individuell – Grund: Solarthermie vorhanden (Stilllegung)</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
+          <t>Artikel: Z24 ×1</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Rückbau im Heizungsraum, 0,00 € (v9)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6687,7 +6745,6 @@
           <t>AMPEL: individuell – Grund: Größe des Pufferspeichers nicht konfigurierbar</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6945,7 +7002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7593,6 +7650,34 @@
       <c r="F24" t="inlineStr">
         <is>
           <t>3-Phasen Stromzähler mit MID zur privaten Verbrauchsmessung einer Wohneinheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Z24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rückbau Solarthermieanlage im Heizungsraum inkl. Entsorgung</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>psl.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Technischer Hinweis: Im Angebot enthalten ist ausschließlich der Rückbau der Solarthermieanlage im Heizungsraum, einschließlich Aufputzleitungen, Solarthermie-Speicher und Solarstation, inkl. fachgerechter Entsorgung. Die vorhandene Solarthermieflüssigkeit wird abgelassen, die Anlage entleert und das Medium fachgerecht entsorgt. Nicht enthalten sind die dachseitigen Komponenten sowie die Leitungsführung außerhalb des Heizungsraums ab dem Übergabepunkt.</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7841,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003 · Serie CS8800i: 030 / 031 · 055 / 056 (N07/N08) · 067</t>
+          <t>WP-Paket lt. Paketmatrix · Puffer (N06) · ggf. Pos. 065 · Pos. 003 · Serie CS8800i: 030 / 031 · 055 / 056 (N07/N08) · 067 · Solar-Übernahme: 069</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -7844,7 +7929,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG) · ggf. Stemmarbeiten Pos. 126</t>
+          <t>Pos. 009 · Öltank-Entsorgung (Z01–Z14 / Pos. 107) · Pos. 163 (bei A04 = DG) · ggf. Stemmarbeiten Pos. 126 · Solarthermie-Rückbau Z24</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
